--- a/artfynd/A 1924-2025 artfynd.xlsx
+++ b/artfynd/A 1924-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122215762</v>
+        <v>122215746</v>
       </c>
       <c r="B2" t="n">
-        <v>95738</v>
+        <v>57525</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372394</v>
+        <v>372311</v>
       </c>
       <c r="R2" t="n">
-        <v>6413616</v>
+        <v>6413509</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -778,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122215761</v>
+        <v>122215755</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>97111</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372488</v>
+        <v>372437</v>
       </c>
       <c r="R3" t="n">
-        <v>6413342</v>
+        <v>6413491</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122215750</v>
+        <v>122215739</v>
       </c>
       <c r="B4" t="n">
-        <v>96682</v>
+        <v>94569</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372313</v>
+        <v>372454</v>
       </c>
       <c r="R4" t="n">
-        <v>6413510</v>
+        <v>6413485</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122215753</v>
+        <v>122215751</v>
       </c>
       <c r="B5" t="n">
-        <v>57385</v>
+        <v>96690</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -994,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1022,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372398</v>
+        <v>372445</v>
       </c>
       <c r="R5" t="n">
-        <v>6413615</v>
+        <v>6413602</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122215755</v>
+        <v>122215753</v>
       </c>
       <c r="B6" t="n">
-        <v>97103</v>
+        <v>57388</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1096,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372437</v>
+        <v>372398</v>
       </c>
       <c r="R6" t="n">
-        <v>6413491</v>
+        <v>6413615</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1188,7 @@
         <v>122215754</v>
       </c>
       <c r="B7" t="n">
-        <v>57385</v>
+        <v>57388</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122214987</v>
+        <v>122215761</v>
       </c>
       <c r="B8" t="n">
-        <v>57522</v>
+        <v>57742</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1300,53 +1299,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundsmossen, Vg</t>
+          <t>Mjöshult, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372458</v>
+        <v>372488</v>
       </c>
       <c r="R8" t="n">
-        <v>6413571</v>
+        <v>6413342</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1373,19 +1360,9 @@
           <t>2025-01-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,12 +1377,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo Hultgren, Erik Vikstrand</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johannes Stolt, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1415,7 +1392,7 @@
         <v>122215738</v>
       </c>
       <c r="B9" t="n">
-        <v>94561</v>
+        <v>94569</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122215751</v>
+        <v>122215762</v>
       </c>
       <c r="B10" t="n">
-        <v>96682</v>
+        <v>95746</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1530,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>2590</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372445</v>
+        <v>372394</v>
       </c>
       <c r="R10" t="n">
-        <v>6413602</v>
+        <v>6413616</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,6 +1575,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1616,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122215760</v>
+        <v>122215750</v>
       </c>
       <c r="B11" t="n">
-        <v>57738</v>
+        <v>96690</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1632,21 +1610,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1656,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372508</v>
+        <v>372313</v>
       </c>
       <c r="R11" t="n">
-        <v>6413498</v>
+        <v>6413510</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,10 +1696,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122215739</v>
+        <v>122215760</v>
       </c>
       <c r="B12" t="n">
-        <v>94561</v>
+        <v>57742</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1734,21 +1712,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2810</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1758,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372454</v>
+        <v>372508</v>
       </c>
       <c r="R12" t="n">
-        <v>6413485</v>
+        <v>6413498</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122215749</v>
+        <v>122214987</v>
       </c>
       <c r="B13" t="n">
-        <v>96682</v>
+        <v>57525</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1832,41 +1810,53 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mjöshult, Vg</t>
+          <t>Sundsmossen, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372299</v>
+        <v>372458</v>
       </c>
       <c r="R13" t="n">
-        <v>6413369</v>
+        <v>6413571</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1893,9 +1883,19 @@
           <t>2025-01-19</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1910,22 +1910,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Bo Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johannes Stolt, Johan Linderstad</t>
+          <t>Bo Hultgren, Erik Vikstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122215746</v>
+        <v>122215749</v>
       </c>
       <c r="B14" t="n">
-        <v>57522</v>
+        <v>96690</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1934,25 +1934,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>372311</v>
+        <v>372299</v>
       </c>
       <c r="R14" t="n">
-        <v>6413509</v>
+        <v>6413369</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 1924-2025 artfynd.xlsx
+++ b/artfynd/A 1924-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122215738</v>
+        <v>122215751</v>
       </c>
       <c r="B2" t="n">
-        <v>94587</v>
+        <v>96708</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372444</v>
+        <v>372445</v>
       </c>
       <c r="R2" t="n">
-        <v>6413595</v>
+        <v>6413602</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122215750</v>
+        <v>122215749</v>
       </c>
       <c r="B3" t="n">
         <v>96708</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372313</v>
+        <v>372299</v>
       </c>
       <c r="R3" t="n">
-        <v>6413510</v>
+        <v>6413369</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122215761</v>
+        <v>122215753</v>
       </c>
       <c r="B4" t="n">
-        <v>57744</v>
+        <v>57390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,20 +891,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372488</v>
+        <v>372398</v>
       </c>
       <c r="R4" t="n">
-        <v>6413342</v>
+        <v>6413615</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122215751</v>
+        <v>122215754</v>
       </c>
       <c r="B5" t="n">
-        <v>96708</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372445</v>
+        <v>372471</v>
       </c>
       <c r="R5" t="n">
-        <v>6413602</v>
+        <v>6413575</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122215753</v>
+        <v>122215755</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>97129</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372398</v>
+        <v>372437</v>
       </c>
       <c r="R6" t="n">
-        <v>6413615</v>
+        <v>6413491</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122215760</v>
+        <v>122215750</v>
       </c>
       <c r="B7" t="n">
-        <v>57744</v>
+        <v>96708</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372508</v>
+        <v>372313</v>
       </c>
       <c r="R7" t="n">
-        <v>6413498</v>
+        <v>6413510</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122215754</v>
+        <v>122215760</v>
       </c>
       <c r="B8" t="n">
-        <v>57390</v>
+        <v>57744</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,20 +1299,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372471</v>
+        <v>372508</v>
       </c>
       <c r="R8" t="n">
-        <v>6413575</v>
+        <v>6413498</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122215749</v>
+        <v>122215761</v>
       </c>
       <c r="B9" t="n">
-        <v>96708</v>
+        <v>57744</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372299</v>
+        <v>372488</v>
       </c>
       <c r="R9" t="n">
-        <v>6413369</v>
+        <v>6413342</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122214987</v>
+        <v>122215746</v>
       </c>
       <c r="B10" t="n">
         <v>57527</v>
@@ -1524,32 +1524,20 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sundsmossen, Vg</t>
+          <t>Mjöshult, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372458</v>
+        <v>372311</v>
       </c>
       <c r="R10" t="n">
-        <v>6413571</v>
+        <v>6413509</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1576,19 +1564,9 @@
           <t>2025-01-19</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,22 +1581,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo Hultgren, Erik Vikstrand</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122215755</v>
+        <v>122214987</v>
       </c>
       <c r="B11" t="n">
-        <v>97129</v>
+        <v>57527</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1627,41 +1605,53 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mjöshult, Vg</t>
+          <t>Sundsmossen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372437</v>
+        <v>372458</v>
       </c>
       <c r="R11" t="n">
-        <v>6413491</v>
+        <v>6413571</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1688,9 +1678,19 @@
           <t>2025-01-19</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,12 +1705,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Bo Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
+          <t>Bo Hultgren, Erik Vikstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122215746</v>
+        <v>122215738</v>
       </c>
       <c r="B13" t="n">
-        <v>57527</v>
+        <v>94587</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1831,25 +1831,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>2810</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372311</v>
+        <v>372444</v>
       </c>
       <c r="R13" t="n">
-        <v>6413509</v>
+        <v>6413595</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 1924-2025 artfynd.xlsx
+++ b/artfynd/A 1924-2025 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122215754</v>
+        <v>122215755</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>97129</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372471</v>
+        <v>372437</v>
       </c>
       <c r="R5" t="n">
-        <v>6413575</v>
+        <v>6413491</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122215755</v>
+        <v>122215754</v>
       </c>
       <c r="B6" t="n">
-        <v>97129</v>
+        <v>57390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372437</v>
+        <v>372471</v>
       </c>
       <c r="R6" t="n">
-        <v>6413491</v>
+        <v>6413575</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 1924-2025 artfynd.xlsx
+++ b/artfynd/A 1924-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122215751</v>
+        <v>122215753</v>
       </c>
       <c r="B2" t="n">
-        <v>96708</v>
+        <v>57390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372445</v>
+        <v>372398</v>
       </c>
       <c r="R2" t="n">
-        <v>6413602</v>
+        <v>6413615</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,17 +770,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
+          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122215749</v>
+        <v>122215738</v>
       </c>
       <c r="B3" t="n">
-        <v>96708</v>
+        <v>94597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372299</v>
+        <v>372444</v>
       </c>
       <c r="R3" t="n">
-        <v>6413369</v>
+        <v>6413595</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,14 +872,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
+          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122215753</v>
+        <v>122215754</v>
       </c>
       <c r="B4" t="n">
         <v>57390</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372398</v>
+        <v>372471</v>
       </c>
       <c r="R4" t="n">
-        <v>6413615</v>
+        <v>6413575</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,17 +974,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
+          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122215755</v>
+        <v>122215760</v>
       </c>
       <c r="B5" t="n">
-        <v>97129</v>
+        <v>57744</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372437</v>
+        <v>372508</v>
       </c>
       <c r="R5" t="n">
-        <v>6413491</v>
+        <v>6413498</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
+          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122215754</v>
+        <v>122215751</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>96718</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372471</v>
+        <v>372445</v>
       </c>
       <c r="R6" t="n">
-        <v>6413575</v>
+        <v>6413602</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
+          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122215750</v>
+        <v>122215749</v>
       </c>
       <c r="B7" t="n">
-        <v>96708</v>
+        <v>96718</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372313</v>
+        <v>372299</v>
       </c>
       <c r="R7" t="n">
-        <v>6413510</v>
+        <v>6413369</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
+          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122215760</v>
+        <v>122214987</v>
       </c>
       <c r="B8" t="n">
-        <v>57744</v>
+        <v>57527</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,41 +1299,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mjöshult, Vg</t>
+          <t>Sundsmossen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372508</v>
+        <v>372458</v>
       </c>
       <c r="R8" t="n">
-        <v>6413498</v>
+        <v>6413571</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1360,9 +1372,19 @@
           <t>2025-01-19</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,12 +1399,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Bo Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
+          <t>Bo Hultgren, Erik Vikstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1484,17 +1506,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
+          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122215746</v>
+        <v>122215739</v>
       </c>
       <c r="B10" t="n">
-        <v>57527</v>
+        <v>94597</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1525,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372311</v>
+        <v>372454</v>
       </c>
       <c r="R10" t="n">
-        <v>6413509</v>
+        <v>6413485</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,17 +1608,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
+          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122214987</v>
+        <v>122215750</v>
       </c>
       <c r="B11" t="n">
-        <v>57527</v>
+        <v>96718</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,53 +1627,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sundsmossen, Vg</t>
+          <t>Mjöshult, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372458</v>
+        <v>372313</v>
       </c>
       <c r="R11" t="n">
-        <v>6413571</v>
+        <v>6413510</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1678,19 +1688,9 @@
           <t>2025-01-19</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,22 +1705,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo Hultgren, Erik Vikstrand</t>
+          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122215739</v>
+        <v>122215746</v>
       </c>
       <c r="B12" t="n">
-        <v>94587</v>
+        <v>57527</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1729,25 +1729,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1757,10 +1757,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372454</v>
+        <v>372311</v>
       </c>
       <c r="R12" t="n">
-        <v>6413485</v>
+        <v>6413509</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,17 +1812,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
+          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122215738</v>
+        <v>122215755</v>
       </c>
       <c r="B13" t="n">
-        <v>94587</v>
+        <v>97139</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1835,21 +1835,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372444</v>
+        <v>372437</v>
       </c>
       <c r="R13" t="n">
-        <v>6413595</v>
+        <v>6413491</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
+          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1924,7 +1924,7 @@
         <v>122215762</v>
       </c>
       <c r="B14" t="n">
-        <v>95764</v>
+        <v>95774</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
+          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 1924-2025 artfynd.xlsx
+++ b/artfynd/A 1924-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122215753</v>
+        <v>122215739</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>94597</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372398</v>
+        <v>372454</v>
       </c>
       <c r="R2" t="n">
-        <v>6413615</v>
+        <v>6413485</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,17 +770,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122215738</v>
+        <v>122215754</v>
       </c>
       <c r="B3" t="n">
-        <v>94597</v>
+        <v>57390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372444</v>
+        <v>372471</v>
       </c>
       <c r="R3" t="n">
-        <v>6413595</v>
+        <v>6413575</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122215754</v>
+        <v>122215760</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>57744</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,20 +891,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372471</v>
+        <v>372508</v>
       </c>
       <c r="R4" t="n">
-        <v>6413575</v>
+        <v>6413498</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,17 +974,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122215760</v>
+        <v>122215755</v>
       </c>
       <c r="B5" t="n">
-        <v>57744</v>
+        <v>97139</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372508</v>
+        <v>372437</v>
       </c>
       <c r="R5" t="n">
-        <v>6413498</v>
+        <v>6413491</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122215751</v>
+        <v>122215761</v>
       </c>
       <c r="B6" t="n">
-        <v>96718</v>
+        <v>57744</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372445</v>
+        <v>372488</v>
       </c>
       <c r="R6" t="n">
-        <v>6413602</v>
+        <v>6413342</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,14 +1178,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122215749</v>
+        <v>122215751</v>
       </c>
       <c r="B7" t="n">
         <v>96718</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372299</v>
+        <v>372445</v>
       </c>
       <c r="R7" t="n">
-        <v>6413369</v>
+        <v>6413602</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122214987</v>
+        <v>122215749</v>
       </c>
       <c r="B8" t="n">
-        <v>57527</v>
+        <v>96718</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,53 +1299,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundsmossen, Vg</t>
+          <t>Mjöshult, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372458</v>
+        <v>372299</v>
       </c>
       <c r="R8" t="n">
-        <v>6413571</v>
+        <v>6413369</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1372,19 +1360,9 @@
           <t>2025-01-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo Hultgren, Erik Vikstrand</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122215761</v>
+        <v>122215746</v>
       </c>
       <c r="B9" t="n">
-        <v>57744</v>
+        <v>57527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372488</v>
+        <v>372311</v>
       </c>
       <c r="R9" t="n">
-        <v>6413342</v>
+        <v>6413509</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,17 +1484,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122215739</v>
+        <v>122214987</v>
       </c>
       <c r="B10" t="n">
-        <v>94597</v>
+        <v>57527</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,41 +1503,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mjöshult, Vg</t>
+          <t>Sundsmossen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372454</v>
+        <v>372458</v>
       </c>
       <c r="R10" t="n">
-        <v>6413485</v>
+        <v>6413571</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1586,9 +1576,19 @@
           <t>2025-01-19</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,22 +1603,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Bo Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
+          <t>Bo Hultgren, Erik Vikstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122215750</v>
+        <v>122215738</v>
       </c>
       <c r="B11" t="n">
-        <v>96718</v>
+        <v>94597</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1631,21 +1631,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372313</v>
+        <v>372444</v>
       </c>
       <c r="R11" t="n">
-        <v>6413510</v>
+        <v>6413595</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,17 +1710,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122215746</v>
+        <v>122215753</v>
       </c>
       <c r="B12" t="n">
-        <v>57527</v>
+        <v>57390</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1733,21 +1733,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1757,10 +1757,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372311</v>
+        <v>372398</v>
       </c>
       <c r="R12" t="n">
-        <v>6413509</v>
+        <v>6413615</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,17 +1812,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122215755</v>
+        <v>122215750</v>
       </c>
       <c r="B13" t="n">
-        <v>97139</v>
+        <v>96718</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1835,21 +1835,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372437</v>
+        <v>372313</v>
       </c>
       <c r="R13" t="n">
-        <v>6413491</v>
+        <v>6413510</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Johan Linderstad, Bo Hultgren, Erik Vikstrand, Börje Fritzson, Maria  Werner</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 1924-2025 artfynd.xlsx
+++ b/artfynd/A 1924-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122215739</v>
+        <v>122215746</v>
       </c>
       <c r="B2" t="n">
-        <v>94597</v>
+        <v>57532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372454</v>
+        <v>372311</v>
       </c>
       <c r="R2" t="n">
-        <v>6413485</v>
+        <v>6413509</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122215754</v>
+        <v>122215739</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>94609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372471</v>
+        <v>372454</v>
       </c>
       <c r="R3" t="n">
-        <v>6413575</v>
+        <v>6413485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122215760</v>
+        <v>122215751</v>
       </c>
       <c r="B4" t="n">
-        <v>57744</v>
+        <v>96730</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372508</v>
+        <v>372445</v>
       </c>
       <c r="R4" t="n">
-        <v>6413498</v>
+        <v>6413602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122215755</v>
+        <v>122215749</v>
       </c>
       <c r="B5" t="n">
-        <v>97139</v>
+        <v>96730</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372437</v>
+        <v>372299</v>
       </c>
       <c r="R5" t="n">
-        <v>6413491</v>
+        <v>6413369</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122215761</v>
+        <v>122215753</v>
       </c>
       <c r="B6" t="n">
-        <v>57744</v>
+        <v>57395</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,20 +1095,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372488</v>
+        <v>372398</v>
       </c>
       <c r="R6" t="n">
-        <v>6413342</v>
+        <v>6413615</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122215751</v>
+        <v>122215754</v>
       </c>
       <c r="B7" t="n">
-        <v>96718</v>
+        <v>57395</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372445</v>
+        <v>372471</v>
       </c>
       <c r="R7" t="n">
-        <v>6413602</v>
+        <v>6413575</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122215749</v>
+        <v>122215755</v>
       </c>
       <c r="B8" t="n">
-        <v>96718</v>
+        <v>97151</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372299</v>
+        <v>372437</v>
       </c>
       <c r="R8" t="n">
-        <v>6413369</v>
+        <v>6413491</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122215746</v>
+        <v>122214987</v>
       </c>
       <c r="B9" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1422,20 +1422,32 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mjöshult, Vg</t>
+          <t>Sundsmossen, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372311</v>
+        <v>372458</v>
       </c>
       <c r="R9" t="n">
-        <v>6413509</v>
+        <v>6413571</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1462,9 +1474,19 @@
           <t>2025-01-19</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,22 +1501,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Bo Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
+          <t>Bo Hultgren, Erik Vikstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122214987</v>
+        <v>122215760</v>
       </c>
       <c r="B10" t="n">
-        <v>57527</v>
+        <v>57749</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,53 +1525,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sundsmossen, Vg</t>
+          <t>Mjöshult, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372458</v>
+        <v>372508</v>
       </c>
       <c r="R10" t="n">
-        <v>6413571</v>
+        <v>6413498</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1576,19 +1586,9 @@
           <t>2025-01-19</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,22 +1603,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo Hultgren, Erik Vikstrand</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122215738</v>
+        <v>122215761</v>
       </c>
       <c r="B11" t="n">
-        <v>94597</v>
+        <v>57749</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1631,21 +1631,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372444</v>
+        <v>372488</v>
       </c>
       <c r="R11" t="n">
-        <v>6413595</v>
+        <v>6413342</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,10 +1717,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122215753</v>
+        <v>122215750</v>
       </c>
       <c r="B12" t="n">
-        <v>57390</v>
+        <v>96730</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1729,25 +1729,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1757,10 +1757,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372398</v>
+        <v>372313</v>
       </c>
       <c r="R12" t="n">
-        <v>6413615</v>
+        <v>6413510</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122215750</v>
+        <v>122215738</v>
       </c>
       <c r="B13" t="n">
-        <v>96718</v>
+        <v>94609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1835,21 +1835,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372313</v>
+        <v>372444</v>
       </c>
       <c r="R13" t="n">
-        <v>6413510</v>
+        <v>6413595</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,7 +1924,7 @@
         <v>122215762</v>
       </c>
       <c r="B14" t="n">
-        <v>95774</v>
+        <v>95786</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 1924-2025 artfynd.xlsx
+++ b/artfynd/A 1924-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122215746</v>
+        <v>122215738</v>
       </c>
       <c r="B2" t="n">
-        <v>57532</v>
+        <v>94614</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372311</v>
+        <v>372444</v>
       </c>
       <c r="R2" t="n">
-        <v>6413509</v>
+        <v>6413595</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122215739</v>
+        <v>122215750</v>
       </c>
       <c r="B3" t="n">
-        <v>94609</v>
+        <v>96735</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372454</v>
+        <v>372313</v>
       </c>
       <c r="R3" t="n">
-        <v>6413485</v>
+        <v>6413510</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122215751</v>
+        <v>122215739</v>
       </c>
       <c r="B4" t="n">
-        <v>96730</v>
+        <v>94614</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372445</v>
+        <v>372454</v>
       </c>
       <c r="R4" t="n">
-        <v>6413602</v>
+        <v>6413485</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122215749</v>
+        <v>122215753</v>
       </c>
       <c r="B5" t="n">
-        <v>96730</v>
+        <v>57395</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372299</v>
+        <v>372398</v>
       </c>
       <c r="R5" t="n">
-        <v>6413369</v>
+        <v>6413615</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122215753</v>
+        <v>122215761</v>
       </c>
       <c r="B6" t="n">
-        <v>57395</v>
+        <v>57749</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,20 +1095,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372398</v>
+        <v>372488</v>
       </c>
       <c r="R6" t="n">
-        <v>6413615</v>
+        <v>6413342</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122215755</v>
+        <v>122215751</v>
       </c>
       <c r="B8" t="n">
-        <v>97151</v>
+        <v>96735</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372437</v>
+        <v>372445</v>
       </c>
       <c r="R8" t="n">
-        <v>6413491</v>
+        <v>6413602</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122215760</v>
+        <v>122215749</v>
       </c>
       <c r="B10" t="n">
-        <v>57749</v>
+        <v>96735</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,21 +1529,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372508</v>
+        <v>372299</v>
       </c>
       <c r="R10" t="n">
-        <v>6413498</v>
+        <v>6413369</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,10 +1615,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122215761</v>
+        <v>122215755</v>
       </c>
       <c r="B11" t="n">
-        <v>57749</v>
+        <v>97156</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1631,21 +1631,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372488</v>
+        <v>372437</v>
       </c>
       <c r="R11" t="n">
-        <v>6413342</v>
+        <v>6413491</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,10 +1717,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122215750</v>
+        <v>122215760</v>
       </c>
       <c r="B12" t="n">
-        <v>96730</v>
+        <v>57749</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1733,21 +1733,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1757,10 +1757,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372313</v>
+        <v>372508</v>
       </c>
       <c r="R12" t="n">
-        <v>6413510</v>
+        <v>6413498</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122215738</v>
+        <v>122215746</v>
       </c>
       <c r="B13" t="n">
-        <v>94609</v>
+        <v>57532</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1831,25 +1831,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372444</v>
+        <v>372311</v>
       </c>
       <c r="R13" t="n">
-        <v>6413595</v>
+        <v>6413509</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,7 +1924,7 @@
         <v>122215762</v>
       </c>
       <c r="B14" t="n">
-        <v>95786</v>
+        <v>95791</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 1924-2025 artfynd.xlsx
+++ b/artfynd/A 1924-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122215738</v>
+        <v>122215753</v>
       </c>
       <c r="B2" t="n">
-        <v>94614</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372444</v>
+        <v>372398</v>
       </c>
       <c r="R2" t="n">
-        <v>6413595</v>
+        <v>6413615</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122215750</v>
+        <v>122214987</v>
       </c>
       <c r="B3" t="n">
-        <v>96735</v>
+        <v>57532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +784,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Stor revmossa</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mjöshult, Vg</t>
+          <t>Sundsmossen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372313</v>
+        <v>372458</v>
       </c>
       <c r="R3" t="n">
-        <v>6413510</v>
+        <v>6413571</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,9 +852,19 @@
           <t>2025-01-19</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +879,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Bo Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
+          <t>Bo Hultgren, Erik Vikstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122215739</v>
+        <v>122215749</v>
       </c>
       <c r="B4" t="n">
-        <v>94614</v>
+        <v>96744</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +907,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa</t>
-        </is>
+        <v>2569</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372454</v>
+        <v>372299</v>
       </c>
       <c r="R4" t="n">
-        <v>6413485</v>
+        <v>6413369</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +988,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122215753</v>
+        <v>122215754</v>
       </c>
       <c r="B5" t="n">
         <v>57395</v>
@@ -999,11 +1006,6 @@
       <c r="E5" t="n">
         <v>100049</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -1021,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372398</v>
+        <v>372471</v>
       </c>
       <c r="R5" t="n">
-        <v>6413615</v>
+        <v>6413575</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1085,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122215761</v>
+        <v>122215750</v>
       </c>
       <c r="B6" t="n">
-        <v>57749</v>
+        <v>96744</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1101,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>2569</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372488</v>
+        <v>372313</v>
       </c>
       <c r="R6" t="n">
-        <v>6413342</v>
+        <v>6413510</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1182,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122215754</v>
+        <v>122215746</v>
       </c>
       <c r="B7" t="n">
-        <v>57395</v>
+        <v>57532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1198,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372471</v>
+        <v>372311</v>
       </c>
       <c r="R7" t="n">
-        <v>6413575</v>
+        <v>6413509</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1282,7 @@
         <v>122215751</v>
       </c>
       <c r="B8" t="n">
-        <v>96735</v>
+        <v>96744</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,11 +1296,6 @@
       </c>
       <c r="E8" t="n">
         <v>2569</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Stor revmossa</t>
-        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1389,10 +1376,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122214987</v>
+        <v>122215761</v>
       </c>
       <c r="B9" t="n">
-        <v>57532</v>
+        <v>57749</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,53 +1388,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sundsmossen, Vg</t>
+          <t>Mjöshult, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372458</v>
+        <v>372488</v>
       </c>
       <c r="R9" t="n">
-        <v>6413571</v>
+        <v>6413342</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1474,19 +1444,9 @@
           <t>2025-01-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,22 +1461,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo Hultgren, Erik Vikstrand</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122215749</v>
+        <v>122215755</v>
       </c>
       <c r="B10" t="n">
-        <v>96735</v>
+        <v>97165</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,21 +1489,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Stor revmossa</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1508,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372299</v>
+        <v>372437</v>
       </c>
       <c r="R10" t="n">
-        <v>6413369</v>
+        <v>6413491</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,10 +1570,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122215755</v>
+        <v>122215739</v>
       </c>
       <c r="B11" t="n">
-        <v>97156</v>
+        <v>94623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1631,21 +1586,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>2810</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1605,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372437</v>
+        <v>372454</v>
       </c>
       <c r="R11" t="n">
-        <v>6413491</v>
+        <v>6413485</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,11 +1685,6 @@
       <c r="E12" t="n">
         <v>103015</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Regulus regulus</t>
@@ -1819,10 +1764,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122215746</v>
+        <v>122215738</v>
       </c>
       <c r="B13" t="n">
-        <v>57532</v>
+        <v>94623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1831,25 +1776,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>2810</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1859,10 +1799,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372311</v>
+        <v>372444</v>
       </c>
       <c r="R13" t="n">
-        <v>6413509</v>
+        <v>6413595</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,7 +1864,7 @@
         <v>122215762</v>
       </c>
       <c r="B14" t="n">
-        <v>95791</v>
+        <v>95800</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1938,11 +1878,6 @@
       </c>
       <c r="E14" t="n">
         <v>2590</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Kornknutmossa</t>
-        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>

--- a/artfynd/A 1924-2025 artfynd.xlsx
+++ b/artfynd/A 1924-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122215753</v>
+        <v>122215751</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>96757</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2569</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372398</v>
+        <v>372445</v>
       </c>
       <c r="R2" t="n">
-        <v>6413615</v>
+        <v>6413602</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122214987</v>
+        <v>122215760</v>
       </c>
       <c r="B3" t="n">
-        <v>57532</v>
+        <v>57753</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -784,48 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sundsmossen, Vg</t>
+          <t>Mjöshult, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372458</v>
+        <v>372508</v>
       </c>
       <c r="R3" t="n">
-        <v>6413571</v>
+        <v>6413498</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,19 +850,9 @@
           <t>2025-01-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo Hultgren, Erik Vikstrand</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122215749</v>
+        <v>122214987</v>
       </c>
       <c r="B4" t="n">
-        <v>96744</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,36 +891,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mjöshult, Vg</t>
+          <t>Sundsmossen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372299</v>
+        <v>372458</v>
       </c>
       <c r="R4" t="n">
-        <v>6413369</v>
+        <v>6413571</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,9 +964,19 @@
           <t>2025-01-19</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,22 +991,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Bo Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
+          <t>Bo Hultgren, Erik Vikstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122215754</v>
+        <v>122215739</v>
       </c>
       <c r="B5" t="n">
-        <v>57395</v>
+        <v>94636</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1000,20 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2810</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372471</v>
+        <v>372454</v>
       </c>
       <c r="R5" t="n">
-        <v>6413575</v>
+        <v>6413485</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122215750</v>
+        <v>122215754</v>
       </c>
       <c r="B6" t="n">
-        <v>96744</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1097,20 +1117,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1120,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372313</v>
+        <v>372471</v>
       </c>
       <c r="R6" t="n">
-        <v>6413510</v>
+        <v>6413575</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122215746</v>
+        <v>122215755</v>
       </c>
       <c r="B7" t="n">
-        <v>57532</v>
+        <v>97178</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1194,20 +1219,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1217,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372311</v>
+        <v>372437</v>
       </c>
       <c r="R7" t="n">
-        <v>6413509</v>
+        <v>6413491</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122215751</v>
+        <v>122215746</v>
       </c>
       <c r="B8" t="n">
-        <v>96744</v>
+        <v>57536</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1291,20 +1321,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1314,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372445</v>
+        <v>372311</v>
       </c>
       <c r="R8" t="n">
-        <v>6413602</v>
+        <v>6413509</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1376,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122215761</v>
+        <v>122215753</v>
       </c>
       <c r="B9" t="n">
-        <v>57749</v>
+        <v>57399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1388,15 +1423,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1411,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372488</v>
+        <v>372398</v>
       </c>
       <c r="R9" t="n">
-        <v>6413342</v>
+        <v>6413615</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122215755</v>
+        <v>122215761</v>
       </c>
       <c r="B10" t="n">
-        <v>97165</v>
+        <v>57753</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1489,16 +1529,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>103015</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1508,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372437</v>
+        <v>372488</v>
       </c>
       <c r="R10" t="n">
-        <v>6413491</v>
+        <v>6413342</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1570,10 +1615,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122215739</v>
+        <v>122215750</v>
       </c>
       <c r="B11" t="n">
-        <v>94623</v>
+        <v>96757</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1586,16 +1631,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>2569</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1605,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372454</v>
+        <v>372313</v>
       </c>
       <c r="R11" t="n">
-        <v>6413485</v>
+        <v>6413510</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1667,10 +1717,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122215760</v>
+        <v>122215738</v>
       </c>
       <c r="B12" t="n">
-        <v>57749</v>
+        <v>94636</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1683,16 +1733,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>2810</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1702,10 +1757,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372508</v>
+        <v>372444</v>
       </c>
       <c r="R12" t="n">
-        <v>6413498</v>
+        <v>6413595</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1764,10 +1819,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122215738</v>
+        <v>122215749</v>
       </c>
       <c r="B13" t="n">
-        <v>94623</v>
+        <v>96757</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1780,16 +1835,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2810</v>
+        <v>2569</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1799,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372444</v>
+        <v>372299</v>
       </c>
       <c r="R13" t="n">
-        <v>6413595</v>
+        <v>6413369</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1864,7 +1924,7 @@
         <v>122215762</v>
       </c>
       <c r="B14" t="n">
-        <v>95800</v>
+        <v>95813</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1878,6 +1938,11 @@
       </c>
       <c r="E14" t="n">
         <v>2590</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>

--- a/artfynd/A 1924-2025 artfynd.xlsx
+++ b/artfynd/A 1924-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122215751</v>
+        <v>122215746</v>
       </c>
       <c r="B2" t="n">
-        <v>96757</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372445</v>
+        <v>372311</v>
       </c>
       <c r="R2" t="n">
-        <v>6413602</v>
+        <v>6413509</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122215760</v>
+        <v>122215750</v>
       </c>
       <c r="B3" t="n">
-        <v>57753</v>
+        <v>96770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372508</v>
+        <v>372313</v>
       </c>
       <c r="R3" t="n">
-        <v>6413498</v>
+        <v>6413510</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122214987</v>
+        <v>122215751</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>96770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,53 +891,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sundsmossen, Vg</t>
+          <t>Mjöshult, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372458</v>
+        <v>372445</v>
       </c>
       <c r="R4" t="n">
-        <v>6413571</v>
+        <v>6413602</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,19 +952,9 @@
           <t>2025-01-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Hultgren, Erik Vikstrand</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122215739</v>
+        <v>122215754</v>
       </c>
       <c r="B5" t="n">
-        <v>94636</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372454</v>
+        <v>372471</v>
       </c>
       <c r="R5" t="n">
-        <v>6413485</v>
+        <v>6413575</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122215754</v>
+        <v>122215755</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>97191</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1145,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372471</v>
+        <v>372437</v>
       </c>
       <c r="R6" t="n">
-        <v>6413575</v>
+        <v>6413491</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122215755</v>
+        <v>122215760</v>
       </c>
       <c r="B7" t="n">
-        <v>97178</v>
+        <v>57753</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1247,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372437</v>
+        <v>372508</v>
       </c>
       <c r="R7" t="n">
-        <v>6413491</v>
+        <v>6413498</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122215746</v>
+        <v>122215753</v>
       </c>
       <c r="B8" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1349,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372311</v>
+        <v>372398</v>
       </c>
       <c r="R8" t="n">
-        <v>6413509</v>
+        <v>6413615</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122215753</v>
+        <v>122215749</v>
       </c>
       <c r="B9" t="n">
-        <v>57399</v>
+        <v>96770</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372398</v>
+        <v>372299</v>
       </c>
       <c r="R9" t="n">
-        <v>6413615</v>
+        <v>6413369</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122215761</v>
+        <v>122215739</v>
       </c>
       <c r="B10" t="n">
-        <v>57753</v>
+        <v>94649</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372488</v>
+        <v>372454</v>
       </c>
       <c r="R10" t="n">
-        <v>6413342</v>
+        <v>6413485</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122215750</v>
+        <v>122215738</v>
       </c>
       <c r="B11" t="n">
-        <v>96757</v>
+        <v>94649</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1631,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372313</v>
+        <v>372444</v>
       </c>
       <c r="R11" t="n">
-        <v>6413510</v>
+        <v>6413595</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122215738</v>
+        <v>122214987</v>
       </c>
       <c r="B12" t="n">
-        <v>94636</v>
+        <v>57536</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1729,41 +1707,53 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mjöshult, Vg</t>
+          <t>Sundsmossen, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372444</v>
+        <v>372458</v>
       </c>
       <c r="R12" t="n">
-        <v>6413595</v>
+        <v>6413571</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1790,9 +1780,19 @@
           <t>2025-01-19</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,22 +1807,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Bo Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
+          <t>Bo Hultgren, Erik Vikstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122215749</v>
+        <v>122215761</v>
       </c>
       <c r="B13" t="n">
-        <v>96757</v>
+        <v>57753</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1835,21 +1835,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372299</v>
+        <v>372488</v>
       </c>
       <c r="R13" t="n">
-        <v>6413369</v>
+        <v>6413342</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,7 +1924,7 @@
         <v>122215762</v>
       </c>
       <c r="B14" t="n">
-        <v>95813</v>
+        <v>95826</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 1924-2025 artfynd.xlsx
+++ b/artfynd/A 1924-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122215746</v>
+        <v>122214987</v>
       </c>
       <c r="B2" t="n">
         <v>57536</v>
@@ -708,20 +708,32 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mjöshult, Vg</t>
+          <t>Sundsmossen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372311</v>
+        <v>372458</v>
       </c>
       <c r="R2" t="n">
-        <v>6413509</v>
+        <v>6413571</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +760,19 @@
           <t>2025-01-19</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +787,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Bo Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
+          <t>Bo Hultgren, Erik Vikstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122215750</v>
+        <v>122215746</v>
       </c>
       <c r="B3" t="n">
-        <v>96770</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +811,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372313</v>
+        <v>372311</v>
       </c>
       <c r="R3" t="n">
-        <v>6413510</v>
+        <v>6413509</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122215751</v>
+        <v>122215760</v>
       </c>
       <c r="B4" t="n">
-        <v>96770</v>
+        <v>57753</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372445</v>
+        <v>372508</v>
       </c>
       <c r="R4" t="n">
-        <v>6413602</v>
+        <v>6413498</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122215754</v>
+        <v>122215749</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>96770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372471</v>
+        <v>372299</v>
       </c>
       <c r="R5" t="n">
-        <v>6413575</v>
+        <v>6413369</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122215755</v>
+        <v>122215751</v>
       </c>
       <c r="B6" t="n">
-        <v>97191</v>
+        <v>96770</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1121,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372437</v>
+        <v>372445</v>
       </c>
       <c r="R6" t="n">
-        <v>6413491</v>
+        <v>6413602</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122215760</v>
+        <v>122215739</v>
       </c>
       <c r="B7" t="n">
-        <v>57753</v>
+        <v>94649</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1223,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372508</v>
+        <v>372454</v>
       </c>
       <c r="R7" t="n">
-        <v>6413498</v>
+        <v>6413485</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122215753</v>
+        <v>122215750</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>96770</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1321,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372398</v>
+        <v>372313</v>
       </c>
       <c r="R8" t="n">
-        <v>6413615</v>
+        <v>6413510</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122215749</v>
+        <v>122215761</v>
       </c>
       <c r="B9" t="n">
-        <v>96770</v>
+        <v>57753</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1427,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372299</v>
+        <v>372488</v>
       </c>
       <c r="R9" t="n">
-        <v>6413369</v>
+        <v>6413342</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1513,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122215739</v>
+        <v>122215738</v>
       </c>
       <c r="B10" t="n">
         <v>94649</v>
@@ -1531,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372454</v>
+        <v>372444</v>
       </c>
       <c r="R10" t="n">
-        <v>6413485</v>
+        <v>6413595</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1615,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122215738</v>
+        <v>122215753</v>
       </c>
       <c r="B11" t="n">
-        <v>94649</v>
+        <v>57399</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1627,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372444</v>
+        <v>372398</v>
       </c>
       <c r="R11" t="n">
-        <v>6413595</v>
+        <v>6413615</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1717,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122214987</v>
+        <v>122215754</v>
       </c>
       <c r="B12" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,49 +1733,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sundsmossen, Vg</t>
+          <t>Mjöshult, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372458</v>
+        <v>372471</v>
       </c>
       <c r="R12" t="n">
-        <v>6413571</v>
+        <v>6413575</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1780,19 +1790,9 @@
           <t>2025-01-19</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,22 +1807,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo Hultgren, Erik Vikstrand</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122215761</v>
+        <v>122215755</v>
       </c>
       <c r="B13" t="n">
-        <v>57753</v>
+        <v>97191</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1835,21 +1835,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372488</v>
+        <v>372437</v>
       </c>
       <c r="R13" t="n">
-        <v>6413342</v>
+        <v>6413491</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 1924-2025 artfynd.xlsx
+++ b/artfynd/A 1924-2025 artfynd.xlsx
@@ -1513,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122215738</v>
+        <v>122215753</v>
       </c>
       <c r="B10" t="n">
-        <v>94649</v>
+        <v>57399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,25 +1525,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372444</v>
+        <v>372398</v>
       </c>
       <c r="R10" t="n">
-        <v>6413595</v>
+        <v>6413615</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122215753</v>
+        <v>122215754</v>
       </c>
       <c r="B11" t="n">
         <v>57399</v>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372398</v>
+        <v>372471</v>
       </c>
       <c r="R11" t="n">
-        <v>6413615</v>
+        <v>6413575</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,10 +1717,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122215754</v>
+        <v>122215755</v>
       </c>
       <c r="B12" t="n">
-        <v>57399</v>
+        <v>97191</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1729,25 +1729,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1757,10 +1757,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372471</v>
+        <v>372437</v>
       </c>
       <c r="R12" t="n">
-        <v>6413575</v>
+        <v>6413491</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122215755</v>
+        <v>122215738</v>
       </c>
       <c r="B13" t="n">
-        <v>97191</v>
+        <v>94649</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1835,21 +1835,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372437</v>
+        <v>372444</v>
       </c>
       <c r="R13" t="n">
-        <v>6413491</v>
+        <v>6413595</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 1924-2025 artfynd.xlsx
+++ b/artfynd/A 1924-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122214987</v>
+        <v>122215753</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,49 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundsmossen, Vg</t>
+          <t>Mjöshult, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372458</v>
+        <v>372398</v>
       </c>
       <c r="R2" t="n">
-        <v>6413571</v>
+        <v>6413615</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,19 +748,9 @@
           <t>2025-01-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo Hultgren, Erik Vikstrand</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122215746</v>
+        <v>122215761</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>57753</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372311</v>
+        <v>372488</v>
       </c>
       <c r="R3" t="n">
-        <v>6413509</v>
+        <v>6413342</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122215760</v>
+        <v>122215755</v>
       </c>
       <c r="B4" t="n">
-        <v>57753</v>
+        <v>97194</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372508</v>
+        <v>372437</v>
       </c>
       <c r="R4" t="n">
-        <v>6413498</v>
+        <v>6413491</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122215749</v>
+        <v>122215738</v>
       </c>
       <c r="B5" t="n">
-        <v>96770</v>
+        <v>94651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372299</v>
+        <v>372444</v>
       </c>
       <c r="R5" t="n">
-        <v>6413369</v>
+        <v>6413595</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122215751</v>
+        <v>122215746</v>
       </c>
       <c r="B6" t="n">
-        <v>96770</v>
+        <v>57536</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1145,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372445</v>
+        <v>372311</v>
       </c>
       <c r="R6" t="n">
-        <v>6413602</v>
+        <v>6413509</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122215739</v>
+        <v>122214987</v>
       </c>
       <c r="B7" t="n">
-        <v>94649</v>
+        <v>57536</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,41 +1197,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mjöshult, Vg</t>
+          <t>Sundsmossen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372454</v>
+        <v>372458</v>
       </c>
       <c r="R7" t="n">
-        <v>6413485</v>
+        <v>6413571</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,9 +1270,19 @@
           <t>2025-01-19</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,22 +1297,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Bo Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
+          <t>Bo Hultgren, Erik Vikstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122215750</v>
+        <v>122215739</v>
       </c>
       <c r="B8" t="n">
-        <v>96770</v>
+        <v>94651</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,21 +1325,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372313</v>
+        <v>372454</v>
       </c>
       <c r="R8" t="n">
-        <v>6413510</v>
+        <v>6413485</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122215761</v>
+        <v>122215749</v>
       </c>
       <c r="B9" t="n">
-        <v>57753</v>
+        <v>96773</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1427,21 +1427,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372488</v>
+        <v>372299</v>
       </c>
       <c r="R9" t="n">
-        <v>6413342</v>
+        <v>6413369</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122215753</v>
+        <v>122215750</v>
       </c>
       <c r="B10" t="n">
-        <v>57399</v>
+        <v>96773</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,25 +1525,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372398</v>
+        <v>372313</v>
       </c>
       <c r="R10" t="n">
-        <v>6413615</v>
+        <v>6413510</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,10 +1615,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122215754</v>
+        <v>122215751</v>
       </c>
       <c r="B11" t="n">
-        <v>57399</v>
+        <v>96773</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1627,25 +1627,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372471</v>
+        <v>372445</v>
       </c>
       <c r="R11" t="n">
-        <v>6413575</v>
+        <v>6413602</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,10 +1717,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122215755</v>
+        <v>122215760</v>
       </c>
       <c r="B12" t="n">
-        <v>97191</v>
+        <v>57753</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1733,21 +1733,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1757,10 +1757,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372437</v>
+        <v>372508</v>
       </c>
       <c r="R12" t="n">
-        <v>6413491</v>
+        <v>6413498</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122215738</v>
+        <v>122215754</v>
       </c>
       <c r="B13" t="n">
-        <v>94649</v>
+        <v>57399</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1831,25 +1831,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372444</v>
+        <v>372471</v>
       </c>
       <c r="R13" t="n">
-        <v>6413595</v>
+        <v>6413575</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,7 +1924,7 @@
         <v>122215762</v>
       </c>
       <c r="B14" t="n">
-        <v>95826</v>
+        <v>95828</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 1924-2025 artfynd.xlsx
+++ b/artfynd/A 1924-2025 artfynd.xlsx
@@ -1924,7 +1924,7 @@
         <v>122215762</v>
       </c>
       <c r="B14" t="n">
-        <v>95828</v>
+        <v>95829</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 1924-2025 artfynd.xlsx
+++ b/artfynd/A 1924-2025 artfynd.xlsx
@@ -1924,7 +1924,7 @@
         <v>122215762</v>
       </c>
       <c r="B14" t="n">
-        <v>95829</v>
+        <v>95832</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 1924-2025 artfynd.xlsx
+++ b/artfynd/A 1924-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122215753</v>
+        <v>122215749</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372398</v>
+        <v>372299</v>
       </c>
       <c r="R2" t="n">
-        <v>6413615</v>
+        <v>6413369</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122215761</v>
+        <v>122215750</v>
       </c>
       <c r="B3" t="n">
-        <v>57753</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372488</v>
+        <v>372313</v>
       </c>
       <c r="R3" t="n">
-        <v>6413342</v>
+        <v>6413510</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122215755</v>
+        <v>122215751</v>
       </c>
       <c r="B4" t="n">
-        <v>97194</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372437</v>
+        <v>372445</v>
       </c>
       <c r="R4" t="n">
-        <v>6413491</v>
+        <v>6413602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122215738</v>
+        <v>122215762</v>
       </c>
       <c r="B5" t="n">
-        <v>94651</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372444</v>
+        <v>372394</v>
       </c>
       <c r="R5" t="n">
-        <v>6413595</v>
+        <v>6413616</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,6 +1045,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,37 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122215746</v>
+        <v>122215738</v>
       </c>
       <c r="B6" t="n">
-        <v>57536</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372311</v>
+        <v>372444</v>
       </c>
       <c r="R6" t="n">
-        <v>6413509</v>
+        <v>6413595</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,65 +1161,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122214987</v>
+        <v>122215739</v>
       </c>
       <c r="B7" t="n">
-        <v>57536</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundsmossen, Vg</t>
+          <t>Mjöshult, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372458</v>
+        <v>372454</v>
       </c>
       <c r="R7" t="n">
-        <v>6413571</v>
+        <v>6413485</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1270,19 +1229,9 @@
           <t>2025-01-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,27 +1246,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo Hultgren</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Hultgren, Erik Vikstrand</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122215739</v>
+        <v>122215753</v>
       </c>
       <c r="B8" t="n">
-        <v>94651</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1325,21 +1269,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1349,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372454</v>
+        <v>372398</v>
       </c>
       <c r="R8" t="n">
-        <v>6413485</v>
+        <v>6413615</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,15 +1355,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122215749</v>
+        <v>122215754</v>
       </c>
       <c r="B9" t="n">
-        <v>96773</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,21 +1366,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1390,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372299</v>
+        <v>372471</v>
       </c>
       <c r="R9" t="n">
-        <v>6413369</v>
+        <v>6413575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,15 +1452,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122215750</v>
+        <v>122215760</v>
       </c>
       <c r="B10" t="n">
-        <v>96773</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1529,21 +1463,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372313</v>
+        <v>372508</v>
       </c>
       <c r="R10" t="n">
-        <v>6413510</v>
+        <v>6413498</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,15 +1549,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122215751</v>
+        <v>122215761</v>
       </c>
       <c r="B11" t="n">
-        <v>96773</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1631,21 +1560,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372445</v>
+        <v>372488</v>
       </c>
       <c r="R11" t="n">
-        <v>6413602</v>
+        <v>6413342</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,53 +1646,60 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122215760</v>
+        <v>122214987</v>
       </c>
       <c r="B12" t="n">
-        <v>57753</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mjöshult, Vg</t>
+          <t>Sundsmossen, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372508</v>
+        <v>372458</v>
       </c>
       <c r="R12" t="n">
-        <v>6413498</v>
+        <v>6413571</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1790,9 +1726,19 @@
           <t>2025-01-19</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,27 +1753,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Bo Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Börje Fritzson, Erik Vikstrand, Bo Hultgren, Johan Linderstad</t>
+          <t>Bo Hultgren, Erik Vikstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122215754</v>
+        <v>122215746</v>
       </c>
       <c r="B13" t="n">
-        <v>57399</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1835,21 +1776,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1859,10 +1800,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372471</v>
+        <v>372311</v>
       </c>
       <c r="R13" t="n">
-        <v>6413575</v>
+        <v>6413509</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1921,15 +1862,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122215762</v>
+        <v>122215755</v>
       </c>
       <c r="B14" t="n">
-        <v>95832</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1937,21 +1873,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2590</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1961,10 +1897,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>372394</v>
+        <v>372437</v>
       </c>
       <c r="R14" t="n">
-        <v>6413616</v>
+        <v>6413491</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,7 +1941,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1924-2025 artfynd.xlsx
+++ b/artfynd/A 1924-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122215749</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122215750</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122215762</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122215753</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122215746</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122215751</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122215738</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122215739</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122215754</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122215760</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,6 +1795,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122215761</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1859,6 +1919,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122214987</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1956,8 +2021,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122215755</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>